--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -37,10 +32,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生效日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>剩余金额(亿元)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -50,14 +41,22 @@
   </si>
   <si>
     <t>资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复生效日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复到期日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +103,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -152,7 +154,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -184,9 +186,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -218,6 +221,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -393,44 +397,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="8" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
+    <t>到期日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -24,14 +28,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已使用金额(委托投资)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>已使用金额(合计)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>生效日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>剩余金额(亿元)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -44,12 +48,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>批复生效日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>批复到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>已使用金额(指令投资)</t>
   </si>
 </sst>
 </file>
@@ -399,42 +398,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
-    <col min="2" max="2" width="20.90625" customWidth="1"/>
-    <col min="3" max="5" width="19.26953125" customWidth="1"/>
-    <col min="6" max="8" width="17.26953125" customWidth="1"/>
-    <col min="9" max="9" width="19.26953125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="8" width="17.25" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>到期日</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,6 +49,10 @@
   </si>
   <si>
     <t>已使用金额(指令投资)</t>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -397,17 +401,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.125" customWidth="1"/>
     <col min="2" max="2" width="20.875" customWidth="1"/>
     <col min="3" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="6" max="9" width="17.25" customWidth="1"/>
+    <col min="10" max="10" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -430,9 +434,12 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>0</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeMonitorAst.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12165" windowHeight="3000"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="12170" windowHeight="3000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -37,10 +32,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生效日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>剩余金额(亿元)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -50,14 +41,26 @@
   </si>
   <si>
     <t>资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额度使用情况（亿元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复到期日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批复生效日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +96,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -104,6 +113,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -152,7 +164,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -184,9 +196,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -218,6 +231,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -393,47 +407,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="8" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
